--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>Email</t>
   </si>
@@ -85,6 +85,33 @@
   </si>
   <si>
     <t>Youth Club Automation 2262</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 6287</t>
+  </si>
+  <si>
+    <t>VeolaConsidine@yopmail.com</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 196</t>
+  </si>
+  <si>
+    <t>SammieSmitham@yopmail.com</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 4484</t>
+  </si>
+  <si>
+    <t>BennyDickens@yopmail.com</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 8854</t>
+  </si>
+  <si>
+    <t>CassyLubowitz@yopmail.com</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 5874</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1168,6 +1195,46 @@
         <v>4</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Email</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>Youth Club Automation 5874</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 4770</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1235,6 +1238,14 @@
         <v>17</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Email</t>
   </si>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>Youth Club Automation 4770</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 5183</t>
+  </si>
+  <si>
+    <t>AngeleKilbackMD@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1246,6 +1252,14 @@
         <v>12</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Email</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>AngeleKilbackMD@yopmail.com</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 3470</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1260,6 +1263,14 @@
         <v>30</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>Email</t>
   </si>
@@ -127,6 +127,12 @@
   </si>
   <si>
     <t>Youth Club Automation 1473</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 6345</t>
+  </si>
+  <si>
+    <t>HassieBrown@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1282,6 +1288,14 @@
         <v>4</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>Email</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>HassieBrown@yopmail.com</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 4394</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1299,14 @@
         <v>34</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>Email</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>Youth Club Automation 2517</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 8226</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1384,6 +1387,14 @@
         <v>34</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>Email</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Youth Club Automation 8226</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 9435</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1398,14 @@
         <v>34</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
   <si>
     <t>Email</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>Youth Club Automation 9435</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 775</t>
   </si>
 </sst>
 </file>
@@ -1147,7 +1150,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1406,6 +1409,14 @@
         <v>34</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="48">
   <si>
     <t>Email</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>Youth Club Automation 775</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 2320</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 3504</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1417,6 +1423,22 @@
         <v>34</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <t>Email</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>Youth Club Automation 3504</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 742</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1439,6 +1442,14 @@
         <v>34</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
   <si>
     <t>Email</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>Youth Club Automation 742</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 6965</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1450,6 +1453,14 @@
         <v>34</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
   <si>
     <t>Email</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>Youth Club Automation 6965</t>
+  </si>
+  <si>
+    <t>Youth Club Automation 3456</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1461,6 +1464,14 @@
         <v>34</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
   <si>
     <t>Email</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>Prerana Colony Apex Youth Club</t>
+  </si>
+  <si>
+    <t>Sahyog Vihar Nova Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1186,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1530,6 +1533,14 @@
         <v>55</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="61">
   <si>
     <t>Email</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>MissWyattRau@yopmail.com</t>
+  </si>
+  <si>
+    <t>Umang Nagar Nova Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1195,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1555,6 +1558,14 @@
         <v>59</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
   <si>
     <t>Email</t>
   </si>
@@ -214,12 +214,19 @@
   </si>
   <si>
     <t>create_org_09@yopmail.com</t>
+  </si>
+  <si>
+    <t>Yuva Shakti Puram Core Youth Club</t>
+  </si>
+  <si>
+    <t>ChristeenJacobson@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -554,12 +561,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>61</v>
       </c>
     </row>
@@ -571,375 +578,383 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>55</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24980" windowHeight="12200"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23256" windowHeight="12204"/>
   </bookViews>
   <sheets>
     <sheet name="ELP_Users" sheetId="1" r:id="rId1"/>
-    <sheet name="YouthClubData" r:id="rId5" sheetId="2"/>
+    <sheet name="YouthClubData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
   <si>
     <t>Email</t>
   </si>
@@ -208,19 +208,26 @@
   </si>
   <si>
     <t>MissWyattRau@yopmail.com</t>
+  </si>
+  <si>
+    <t>Umang Nagar Nova Youth Club</t>
+  </si>
+  <si>
+    <t>create_org_09@yopmail.com</t>
+  </si>
+  <si>
+    <t>Yuva Shakti Puram Core Youth Club</t>
+  </si>
+  <si>
+    <t>ChristeenJacobson@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,353 +235,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -582,306 +252,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1170,32 +551,37 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s" s="0">
         <v>1</v>
       </c>
@@ -1203,7 +589,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s" s="0">
         <v>3</v>
       </c>
@@ -1211,7 +597,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s" s="0">
         <v>5</v>
       </c>
@@ -1219,7 +605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2">
       <c r="A4" t="s" s="0">
         <v>6</v>
       </c>
@@ -1227,7 +613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5" t="s" s="0">
         <v>7</v>
       </c>
@@ -1235,7 +621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2">
       <c r="A6" t="s" s="0">
         <v>8</v>
       </c>
@@ -1243,7 +629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7" t="s" s="0">
         <v>9</v>
       </c>
@@ -1251,7 +637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2">
       <c r="A8" t="s" s="0">
         <v>11</v>
       </c>
@@ -1259,7 +645,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2">
       <c r="A9" t="s" s="0">
         <v>13</v>
       </c>
@@ -1267,7 +653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2">
       <c r="A10" t="s" s="0">
         <v>15</v>
       </c>
@@ -1275,7 +661,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2">
       <c r="A11" t="s" s="0">
         <v>16</v>
       </c>
@@ -1283,7 +669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2">
       <c r="A12" t="s" s="0">
         <v>18</v>
       </c>
@@ -1291,7 +677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2">
       <c r="A13" t="s" s="0">
         <v>19</v>
       </c>
@@ -1299,7 +685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2">
       <c r="A14" t="s" s="0">
         <v>21</v>
       </c>
@@ -1307,7 +693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2">
       <c r="A15" t="s" s="0">
         <v>23</v>
       </c>
@@ -1315,7 +701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2">
       <c r="A16" t="s" s="0">
         <v>25</v>
       </c>
@@ -1323,7 +709,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2">
       <c r="A17" t="s" s="0">
         <v>27</v>
       </c>
@@ -1331,7 +717,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2">
       <c r="A18" t="s" s="0">
         <v>28</v>
       </c>
@@ -1339,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2">
       <c r="A19" t="s" s="0">
         <v>29</v>
       </c>
@@ -1347,7 +733,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2">
       <c r="A20" t="s" s="0">
         <v>31</v>
       </c>
@@ -1355,7 +741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2">
       <c r="A21" t="s" s="0">
         <v>32</v>
       </c>
@@ -1363,7 +749,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2">
       <c r="A22" t="s" s="0">
         <v>33</v>
       </c>
@@ -1371,7 +757,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2">
       <c r="A23" t="s" s="0">
         <v>35</v>
       </c>
@@ -1379,7 +765,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2">
       <c r="A24" t="s" s="0">
         <v>36</v>
       </c>
@@ -1387,7 +773,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s" s="0">
         <v>37</v>
       </c>
@@ -1395,7 +781,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2">
       <c r="A26" t="s" s="0">
         <v>38</v>
       </c>
@@ -1403,7 +789,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2">
       <c r="A27" t="s" s="0">
         <v>39</v>
       </c>
@@ -1411,7 +797,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2">
       <c r="A28" t="s" s="0">
         <v>40</v>
       </c>
@@ -1419,7 +805,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2">
       <c r="A29" t="s" s="0">
         <v>41</v>
       </c>
@@ -1427,7 +813,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2">
       <c r="A30" t="s" s="0">
         <v>42</v>
       </c>
@@ -1435,7 +821,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2">
       <c r="A31" t="s" s="0">
         <v>43</v>
       </c>
@@ -1443,7 +829,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2">
       <c r="A32" t="s" s="0">
         <v>44</v>
       </c>
@@ -1451,7 +837,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2">
       <c r="A33" t="s" s="0">
         <v>45</v>
       </c>
@@ -1459,7 +845,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2">
       <c r="A34" t="s" s="0">
         <v>46</v>
       </c>
@@ -1467,7 +853,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2">
       <c r="A35" t="s" s="0">
         <v>47</v>
       </c>
@@ -1475,7 +861,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2">
       <c r="A36" t="s" s="0">
         <v>48</v>
       </c>
@@ -1483,7 +869,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2">
       <c r="A37" t="s" s="0">
         <v>49</v>
       </c>
@@ -1491,7 +877,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2">
       <c r="A38" t="s" s="0">
         <v>50</v>
       </c>
@@ -1499,7 +885,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2">
       <c r="A39" t="s" s="0">
         <v>51</v>
       </c>
@@ -1507,7 +893,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2">
       <c r="A40" t="s" s="0">
         <v>52</v>
       </c>
@@ -1515,7 +901,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2">
       <c r="A41" t="s" s="0">
         <v>53</v>
       </c>
@@ -1523,7 +909,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2">
       <c r="A42" t="s" s="0">
         <v>54</v>
       </c>
@@ -1531,7 +917,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2">
       <c r="A43" t="s" s="0">
         <v>56</v>
       </c>
@@ -1539,7 +925,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2">
       <c r="A44" t="s" s="0">
         <v>57</v>
       </c>
@@ -1547,7 +933,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2">
       <c r="A45" t="s" s="0">
         <v>58</v>
       </c>
@@ -1555,7 +941,23 @@
         <v>59</v>
       </c>
     </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="61">
   <si>
     <t>Email</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>MissWyattRau@yopmail.com</t>
+  </si>
+  <si>
+    <t>Pragati Block Alpha Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1195,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1555,6 +1558,14 @@
         <v>59</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="62">
   <si>
     <t>Email</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Pragati Block Alpha Youth Club</t>
+  </si>
+  <si>
+    <t>Navjyoti Ward Sigma Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1198,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1566,6 +1569,14 @@
         <v>59</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
   <si>
     <t>Email</t>
   </si>
@@ -214,6 +214,12 @@
   </si>
   <si>
     <t>Navjyoti Ward Sigma Youth Club</t>
+  </si>
+  <si>
+    <t>Umang Sector Beta Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607041223m6@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1204,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1577,6 +1583,14 @@
         <v>59</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
   <si>
     <t>Email</t>
   </si>
@@ -220,6 +220,18 @@
   </si>
   <si>
     <t>yco2607041223m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Udaan Mohalla Delta Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607041307m7@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Jagriti Sector Nova Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607041444m7@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1591,6 +1603,22 @@
         <v>63</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="74">
   <si>
     <t>Email</t>
   </si>
@@ -232,6 +232,24 @@
   </si>
   <si>
     <t>yco2607041444m7@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Vikas Basti Elite Youth Club</t>
+  </si>
+  <si>
+    <t>ycpartnera50@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Sankalp Enclave Sigma Youth Club</t>
+  </si>
+  <si>
+    <t>ycpartnera2607050024n51@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Sahyog Mohalla Elite Youth Club</t>
+  </si>
+  <si>
+    <t>ycpartnera2607050051n52@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1619,6 +1637,30 @@
         <v>67</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
   <si>
     <t>Email</t>
   </si>
@@ -220,6 +220,12 @@
   </si>
   <si>
     <t>ChristeenJacobson@yopmail.com</t>
+  </si>
+  <si>
+    <t>Navjyoti Puram Nova Youth Club</t>
+  </si>
+  <si>
+    <t>MrsNadiaZboncak@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -578,7 +584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -957,6 +963,14 @@
         <v>63</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="79">
   <si>
     <t>Email</t>
   </si>
@@ -253,12 +253,25 @@
   </si>
   <si>
     <t xml:space="preserve">mayank1@maildrop.cc </t>
+  </si>
+  <si>
+    <t>Umang Mohalla Alpha Youth Club</t>
+  </si>
+  <si>
+    <t>ycpartnera260707093045n53@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Sahyog Enclave Nova Youth Club</t>
+  </si>
+  <si>
+    <t>ycpartnera260707094521n54@maildrop.cc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -593,12 +606,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -609,431 +622,447 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>72</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>73</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Partner_prod.xlsx
+++ b/resources/Partner_prod.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="78">
   <si>
     <t>Email</t>
   </si>
@@ -250,6 +250,18 @@
   </si>
   <si>
     <t>ycpartnera2607050051n52@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Vikas Sector Delta Youth Club</t>
+  </si>
+  <si>
+    <t>ycpartnera260803203818n53@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Sankalp Vihar Elite Youth Club</t>
+  </si>
+  <si>
+    <t>ycpartnera260807101411n54@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1661,6 +1673,22 @@
         <v>73</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
